--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79555</v>
+        <v>79559</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79559</v>
+        <v>79561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79564</v>
+        <v>79567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79567</v>
+        <v>79580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79580</v>
+        <v>79582</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80652</v>
+        <v>80654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79614</v>
+        <v>79615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92238</v>
+        <v>92239</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83526</v>
+        <v>83527</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83526</v>
+        <v>83527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83526</v>
+        <v>83527</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83526</v>
+        <v>83527</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83526</v>
+        <v>83527</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83526</v>
+        <v>83527</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80654</v>
+        <v>80655</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39092-2026 artfynd.xlsx
+++ b/artfynd/A 39092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136930390</v>
       </c>
       <c r="B2" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136931962</v>
       </c>
       <c r="B3" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136931942</v>
       </c>
       <c r="B4" t="n">
-        <v>79615</v>
+        <v>79618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136930851</v>
       </c>
       <c r="B5" t="n">
-        <v>92239</v>
+        <v>92242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136930746</v>
       </c>
       <c r="B6" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136930991</v>
       </c>
       <c r="B7" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136931033</v>
       </c>
       <c r="B8" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136931719</v>
       </c>
       <c r="B9" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136934538</v>
       </c>
       <c r="B10" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934797</v>
       </c>
       <c r="B11" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934878</v>
       </c>
       <c r="B12" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136935667</v>
       </c>
       <c r="B13" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136933829</v>
       </c>
       <c r="B14" t="n">
-        <v>83527</v>
+        <v>83530</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136934265</v>
       </c>
       <c r="B15" t="n">
-        <v>83527</v>
+        <v>83530</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136934765</v>
       </c>
       <c r="B16" t="n">
-        <v>83527</v>
+        <v>83530</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136934848</v>
       </c>
       <c r="B17" t="n">
-        <v>83527</v>
+        <v>83530</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136935420</v>
       </c>
       <c r="B18" t="n">
-        <v>83527</v>
+        <v>83530</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136935600</v>
       </c>
       <c r="B19" t="n">
-        <v>83527</v>
+        <v>83530</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136931128</v>
       </c>
       <c r="B20" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136931645</v>
       </c>
       <c r="B21" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136933962</v>
       </c>
       <c r="B22" t="n">
-        <v>80655</v>
+        <v>80658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136935312</v>
       </c>
       <c r="B23" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136931103</v>
       </c>
       <c r="B24" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136931125</v>
       </c>
       <c r="B25" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136931641</v>
       </c>
       <c r="B26" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
